--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>mix_adjusted_metric</t>
+          <t>size_adjusted_metric</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>mix_effect</t>
+          <t>size_effect</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>size_effect</t>
+          <t>concentration_effect</t>
         </is>
       </c>
     </row>
@@ -458,16 +458,16 @@
         <v>0.061269</v>
       </c>
       <c r="C2" t="n">
-        <v>0.024228</v>
+        <v>0.058193</v>
       </c>
       <c r="D2" t="n">
-        <v>0.023265</v>
+        <v>0.052774</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.035969</v>
+        <v>-0.003383</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.002036</v>
+        <v>-0.005112</v>
       </c>
     </row>
     <row r="3">
@@ -480,16 +480,16 @@
         <v>0.563588</v>
       </c>
       <c r="C3" t="n">
-        <v>0.304499</v>
+        <v>0.438525</v>
       </c>
       <c r="D3" t="n">
-        <v>0.248824</v>
+        <v>0.399179</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.232621</v>
+        <v>-0.122165</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.08214299999999999</v>
+        <v>-0.042244</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>0.717422</v>
       </c>
       <c r="C4" t="n">
-        <v>0.364022</v>
+        <v>0.67789</v>
       </c>
       <c r="D4" t="n">
-        <v>0.287072</v>
+        <v>0.6165079999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.372433</v>
+        <v>-0.042321</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.057917</v>
+        <v>-0.058593</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.061269</v>
+        <v>0.067604</v>
       </c>
       <c r="C2" t="n">
-        <v>0.058193</v>
+        <v>0.06626700000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.052774</v>
+        <v>0.062174</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.003383</v>
+        <v>-0.001005</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.005112</v>
+        <v>-0.004424</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.563588</v>
+        <v>0.766636</v>
       </c>
       <c r="C3" t="n">
-        <v>0.438525</v>
+        <v>0.450627</v>
       </c>
       <c r="D3" t="n">
-        <v>0.399179</v>
+        <v>0.421855</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.122165</v>
+        <v>-0.291763</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.042244</v>
+        <v>-0.053017</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.717422</v>
+        <v>0.864212</v>
       </c>
       <c r="C4" t="n">
-        <v>0.67789</v>
+        <v>0.760296</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6165079999999999</v>
+        <v>0.675715</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.042321</v>
+        <v>-0.102602</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.058593</v>
+        <v>-0.085894</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -458,16 +458,16 @@
         <v>0.067604</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06626700000000001</v>
+        <v>0.06547699999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.062174</v>
+        <v>0.060668</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.001005</v>
+        <v>-0.002426</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.004424</v>
+        <v>-0.004511</v>
       </c>
     </row>
     <row r="3">
@@ -480,16 +480,16 @@
         <v>0.766636</v>
       </c>
       <c r="C3" t="n">
-        <v>0.450627</v>
+        <v>0.411419</v>
       </c>
       <c r="D3" t="n">
-        <v>0.421855</v>
+        <v>0.386567</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.291763</v>
+        <v>-0.331349</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.053017</v>
+        <v>-0.04872</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>0.864212</v>
       </c>
       <c r="C4" t="n">
-        <v>0.760296</v>
+        <v>0.7596850000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.675715</v>
+        <v>0.679728</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.102602</v>
+        <v>-0.10441</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.085894</v>
+        <v>-0.08007400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -455,19 +455,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.067604</v>
+        <v>0.07244399999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06547699999999999</v>
+        <v>0.06721199999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.060668</v>
+        <v>0.064022</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.002426</v>
+        <v>-0.004278</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.004511</v>
+        <v>-0.004144</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.766636</v>
+        <v>0.766024</v>
       </c>
       <c r="C3" t="n">
-        <v>0.411419</v>
+        <v>0.409409</v>
       </c>
       <c r="D3" t="n">
-        <v>0.386567</v>
+        <v>0.385686</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.331349</v>
+        <v>-0.331654</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.04872</v>
+        <v>-0.048684</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.864212</v>
+        <v>0.865683</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7596850000000001</v>
+        <v>0.646715</v>
       </c>
       <c r="D4" t="n">
-        <v>0.679728</v>
+        <v>0.600541</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.10441</v>
+        <v>-0.193477</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08007400000000001</v>
+        <v>-0.07166500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/decomposition_summary.xlsx
+++ b/vignettes/vignette-1/decomposition_summary.xlsx
@@ -458,16 +458,16 @@
         <v>0.07244399999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06721199999999999</v>
+        <v>0.067217</v>
       </c>
       <c r="D2" t="n">
-        <v>0.064022</v>
+        <v>0.06408800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.004278</v>
+        <v>-0.004262</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.004144</v>
+        <v>-0.004094</v>
       </c>
     </row>
     <row r="3">
@@ -480,16 +480,16 @@
         <v>0.766024</v>
       </c>
       <c r="C3" t="n">
-        <v>0.409409</v>
+        <v>0.408942</v>
       </c>
       <c r="D3" t="n">
-        <v>0.385686</v>
+        <v>0.38559</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.331654</v>
+        <v>-0.332446</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.048684</v>
+        <v>-0.047988</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>0.865683</v>
       </c>
       <c r="C4" t="n">
-        <v>0.646715</v>
+        <v>0.646491</v>
       </c>
       <c r="D4" t="n">
-        <v>0.600541</v>
+        <v>0.601285</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.193477</v>
+        <v>-0.19389</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.07166500000000001</v>
+        <v>-0.070508</v>
       </c>
     </row>
   </sheetData>
